--- a/人間（にんげん）.xlsx
+++ b/人間（にんげん）.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\苗欣奕的东西\折跃\Japanese\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{540516C6-08CA-4831-848C-5FE86B48DB31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90FDD888-5D19-4D08-AF73-568257A452B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="人（ひと）" sheetId="6" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="591">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="597">
   <si>
     <t>わたし</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -197,10 +197,6 @@
   </si>
   <si>
     <t>部長</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ぶち</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2858,6 +2854,34 @@
   </si>
   <si>
     <t>しょうにん</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>彼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>彼女</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>かのじょ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>かれ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ぶちょう</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>訓練者</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>くんれんしゃ</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3250,10 +3274,10 @@
         <v>36</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>206</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="18" x14ac:dyDescent="0.45">
@@ -3264,10 +3288,10 @@
         <v>37</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>208</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="18" x14ac:dyDescent="0.45">
@@ -3278,10 +3302,10 @@
         <v>34</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>214</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="18" x14ac:dyDescent="0.45">
@@ -3292,198 +3316,198 @@
         <v>33</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="F5" t="s">
         <v>283</v>
-      </c>
-      <c r="F5" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="18" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>297</v>
-      </c>
       <c r="D6" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="18" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>98</v>
-      </c>
       <c r="D7" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>139</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="18" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>154</v>
-      </c>
       <c r="D8" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>224</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="18" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>186</v>
-      </c>
       <c r="D9" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="F9" s="1" t="s">
         <v>322</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="18" x14ac:dyDescent="0.45">
       <c r="A10" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>188</v>
-      </c>
       <c r="D10" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>329</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="18" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>211</v>
-      </c>
       <c r="D11" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>331</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="18" x14ac:dyDescent="0.45">
       <c r="A12" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>243</v>
-      </c>
       <c r="D12" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="F12" t="s">
         <v>286</v>
-      </c>
-      <c r="F12" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="18" x14ac:dyDescent="0.45">
       <c r="A13" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>251</v>
-      </c>
       <c r="D13" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="F13" s="1" t="s">
         <v>334</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="18" x14ac:dyDescent="0.45">
       <c r="A14" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>229</v>
-      </c>
       <c r="D14" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="F14" s="1" t="s">
         <v>405</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="18" x14ac:dyDescent="0.45">
       <c r="A15" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>293</v>
-      </c>
       <c r="D15" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="F15" t="s">
         <v>408</v>
-      </c>
-      <c r="F15" t="s">
-        <v>409</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="18" x14ac:dyDescent="0.45">
       <c r="D16" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="F16" s="1" t="s">
         <v>327</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="17" spans="4:6" ht="18" x14ac:dyDescent="0.45">
       <c r="D17" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="F17" s="1" t="s">
         <v>420</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>421</v>
       </c>
     </row>
     <row r="18" spans="4:6" ht="18" x14ac:dyDescent="0.45">
       <c r="D18" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="E18" s="1" t="s">
         <v>559</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>560</v>
       </c>
     </row>
   </sheetData>
@@ -3535,7 +3559,7 @@
     </row>
     <row r="4" spans="1:4" ht="18" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="18" x14ac:dyDescent="0.45">
@@ -3573,10 +3597,10 @@
     </row>
     <row r="8" spans="1:4" ht="18" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>583</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>584</v>
       </c>
     </row>
   </sheetData>
@@ -3587,7 +3611,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C10E333-EBA2-4042-9B73-A72F01BAC739}">
-  <dimension ref="A2:C10"/>
+  <dimension ref="A2:C11"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.109375" bestFit="1" customWidth="1"/>
@@ -3598,7 +3622,7 @@
   <sheetData>
     <row r="2" spans="1:3" ht="18" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B2" t="s">
         <v>15</v>
@@ -3606,7 +3630,7 @@
     </row>
     <row r="3" spans="1:3" ht="18" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B3" t="s">
         <v>16</v>
@@ -3636,29 +3660,45 @@
     </row>
     <row r="6" spans="1:3" ht="18" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="18" x14ac:dyDescent="0.45">
+      <c r="A8" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="C8" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="18" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
-        <v>279</v>
+        <v>590</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="C9" t="s">
-        <v>281</v>
+        <v>593</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="18" x14ac:dyDescent="0.45">
       <c r="A10" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="18" x14ac:dyDescent="0.45">
+      <c r="A11" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>506</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="C11" s="3" t="s">
         <v>507</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>508</v>
       </c>
     </row>
   </sheetData>
@@ -3709,18 +3749,18 @@
     </row>
     <row r="6" spans="1:3" ht="18" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>162</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="18" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>257</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>258</v>
       </c>
     </row>
   </sheetData>
@@ -3745,281 +3785,281 @@
   <sheetData>
     <row r="1" spans="1:13" ht="18" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="18" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>217</v>
-      </c>
       <c r="D2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>59</v>
-      </c>
       <c r="H2" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="I2" s="1" t="s">
-        <v>112</v>
-      </c>
       <c r="L2" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="M2" s="1" t="s">
         <v>366</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>367</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="18" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>424</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>426</v>
-      </c>
       <c r="H3" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="I3" s="1" t="s">
         <v>392</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>393</v>
       </c>
       <c r="J3" s="1"/>
       <c r="L3" t="s">
+        <v>376</v>
+      </c>
+      <c r="M3" s="1" t="s">
         <v>377</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>378</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="18" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B4" t="s">
         <v>218</v>
       </c>
-      <c r="B4" t="s">
-        <v>219</v>
-      </c>
       <c r="D4" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H4" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="I4" s="1" t="s">
         <v>402</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>403</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="18" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>197</v>
-      </c>
       <c r="D5" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>522</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>523</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>524</v>
-      </c>
       <c r="H5" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>422</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="18" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>361</v>
-      </c>
       <c r="D6" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>525</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>526</v>
-      </c>
       <c r="H6" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="I6" s="1" t="s">
         <v>557</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>558</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="18" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>357</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="18" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="C8" t="s">
         <v>231</v>
       </c>
-      <c r="C8" t="s">
-        <v>232</v>
-      </c>
       <c r="D8" t="s">
+        <v>464</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>465</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>466</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="18" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>342</v>
-      </c>
       <c r="D9" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>467</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>468</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="18" x14ac:dyDescent="0.45">
       <c r="A10" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>347</v>
-      </c>
       <c r="D10" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="F10" s="1" t="s">
         <v>473</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>474</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="18" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>353</v>
-      </c>
       <c r="D11" t="s">
+        <v>63</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="F11" t="s">
         <v>65</v>
-      </c>
-      <c r="F11" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="18" x14ac:dyDescent="0.45">
       <c r="A12" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>527</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>528</v>
-      </c>
       <c r="D12" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="F12" s="1" t="s">
         <v>277</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="18" x14ac:dyDescent="0.45">
       <c r="A13" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D13" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>128</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="18" x14ac:dyDescent="0.45">
       <c r="A14" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D14" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>130</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="18" x14ac:dyDescent="0.45">
       <c r="A15" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>538</v>
-      </c>
       <c r="D15" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>483</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="18" x14ac:dyDescent="0.45">
       <c r="A16" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>174</v>
-      </c>
       <c r="D16" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="18" x14ac:dyDescent="0.45">
@@ -4030,13 +4070,13 @@
         <v>28</v>
       </c>
       <c r="D17" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="F17" t="s">
         <v>442</v>
-      </c>
-      <c r="F17" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="18" x14ac:dyDescent="0.45">
@@ -4047,285 +4087,285 @@
         <v>30</v>
       </c>
       <c r="D18" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="E18" s="1" t="s">
         <v>509</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>510</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="18" x14ac:dyDescent="0.45">
       <c r="A19" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="D19" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="E19" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="E19" s="1" t="s">
+      <c r="F19" s="1" t="s">
         <v>494</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>495</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="18" x14ac:dyDescent="0.45">
       <c r="A20" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="B20" s="1" t="s">
-        <v>349</v>
-      </c>
       <c r="C20" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D20" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="E20" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="E20" s="1" t="s">
-        <v>515</v>
-      </c>
       <c r="F20" s="1" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="18" x14ac:dyDescent="0.45">
       <c r="A21" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="B21" s="1" t="s">
-        <v>351</v>
-      </c>
       <c r="D21" t="s">
+        <v>462</v>
+      </c>
+      <c r="E21" t="s">
+        <v>461</v>
+      </c>
+      <c r="F21" t="s">
         <v>463</v>
-      </c>
-      <c r="E21" t="s">
-        <v>462</v>
-      </c>
-      <c r="F21" t="s">
-        <v>464</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="18" x14ac:dyDescent="0.45">
       <c r="A22" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>355</v>
-      </c>
       <c r="C22" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D22" t="s">
+        <v>495</v>
+      </c>
+      <c r="E22" s="1" t="s">
         <v>496</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="F22" s="1" t="s">
         <v>497</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>498</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="18" x14ac:dyDescent="0.45">
       <c r="A23" s="1" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C23" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="D23" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="E23" s="1" t="s">
         <v>519</v>
       </c>
-      <c r="E23" s="1" t="s">
+      <c r="F23" s="1" t="s">
         <v>520</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="18" x14ac:dyDescent="0.45">
       <c r="A24" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="D24" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E24" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="E24" s="1" t="s">
-        <v>110</v>
-      </c>
       <c r="F24" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="18" x14ac:dyDescent="0.45">
       <c r="A25" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D25" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="E25" s="1" t="s">
         <v>516</v>
       </c>
-      <c r="E25" s="1" t="s">
+      <c r="F25" s="1" t="s">
         <v>517</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>518</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="18" x14ac:dyDescent="0.45">
       <c r="A26" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>552</v>
       </c>
-      <c r="B26" s="1" t="s">
-        <v>553</v>
-      </c>
       <c r="D26" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="E26" s="1" t="s">
         <v>571</v>
       </c>
-      <c r="E26" s="1" t="s">
-        <v>572</v>
-      </c>
       <c r="F26" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="18" x14ac:dyDescent="0.45">
       <c r="A27" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="B27" s="1" t="s">
-        <v>245</v>
-      </c>
       <c r="D27" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="E27" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="E27" s="1" t="s">
+      <c r="F27" s="1" t="s">
         <v>534</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>535</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="18" x14ac:dyDescent="0.45">
       <c r="A28" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>554</v>
       </c>
-      <c r="B28" s="1" t="s">
-        <v>555</v>
-      </c>
       <c r="D28" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="E28" s="1" t="s">
         <v>549</v>
       </c>
-      <c r="E28" s="1" t="s">
+      <c r="F28" s="1" t="s">
         <v>550</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>551</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="18" x14ac:dyDescent="0.45">
       <c r="A29" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="B29" s="1" t="s">
-        <v>372</v>
-      </c>
       <c r="C29" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="D29" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="E29" s="1" t="s">
         <v>561</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>562</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="18" x14ac:dyDescent="0.45">
       <c r="A30" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="18" x14ac:dyDescent="0.45">
       <c r="A31" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="B31" s="1" t="s">
         <v>375</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="18" x14ac:dyDescent="0.45">
       <c r="A32" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="B32" s="1" t="s">
         <v>511</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>512</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="18" x14ac:dyDescent="0.45">
       <c r="A33" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="B33" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="C33" s="1" t="s">
         <v>248</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="18" x14ac:dyDescent="0.45">
       <c r="A34" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="B34" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="C34" t="s">
         <v>312</v>
-      </c>
-      <c r="C34" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="18" x14ac:dyDescent="0.45">
       <c r="A35" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="B35" s="1" t="s">
-        <v>363</v>
-      </c>
       <c r="C35" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="18" x14ac:dyDescent="0.45">
       <c r="A36" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C36" t="s">
         <v>235</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="C36" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="18" x14ac:dyDescent="0.45">
       <c r="A37" s="1" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
   </sheetData>
@@ -4336,7 +4376,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{033E45E9-7E3C-4E46-B80D-4D33EE5EAA16}">
-  <dimension ref="A1:S52"/>
+  <dimension ref="A1:S53"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="18.33203125" style="1" bestFit="1" customWidth="1"/>
@@ -4358,1036 +4398,1044 @@
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="G1" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="Q1" s="1" t="s">
         <v>118</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>536</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>45</v>
-      </c>
       <c r="D2" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>86</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>87</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>38</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>39</v>
+        <v>594</v>
       </c>
       <c r="J2" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="K2" s="1" t="s">
-        <v>73</v>
-      </c>
       <c r="N2" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="Q2" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="R2" s="1" t="s">
         <v>314</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G3" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="H3" s="1" t="s">
-        <v>105</v>
-      </c>
       <c r="J3" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="K3" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="K3" s="1" t="s">
-        <v>150</v>
-      </c>
       <c r="N3" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="O3" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="O3" s="1" t="s">
-        <v>92</v>
-      </c>
       <c r="Q3" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="R3" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="R3" s="1" t="s">
+      <c r="S3" s="1" t="s">
         <v>61</v>
-      </c>
-      <c r="S3" s="1" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>49</v>
-      </c>
       <c r="D4" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>100</v>
-      </c>
       <c r="G4" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="H4" s="1" t="s">
-        <v>268</v>
-      </c>
       <c r="J4" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="K4" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="K4" s="1" t="s">
-        <v>289</v>
-      </c>
       <c r="N4" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="O4" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="O4" s="1" t="s">
-        <v>399</v>
-      </c>
       <c r="Q4" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="R4" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>96</v>
-      </c>
       <c r="G5" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N5" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="O5" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="O5" s="1" t="s">
+      <c r="P5" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="P5" s="1" t="s">
-        <v>123</v>
-      </c>
       <c r="Q5" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="R5" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>102</v>
-      </c>
       <c r="G6" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="H6" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="H6" s="1" t="s">
-        <v>107</v>
-      </c>
       <c r="J6" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K6" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="K6" s="1" t="s">
-        <v>75</v>
-      </c>
       <c r="N6" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="O6" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="O6" s="1" t="s">
-        <v>190</v>
-      </c>
       <c r="P6" s="1" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="Q6" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="R6" s="1" t="s">
         <v>124</v>
-      </c>
-      <c r="R6" s="1" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>90</v>
-      </c>
       <c r="D7" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="G7" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="N7" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="O7" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="O7" s="1" t="s">
-        <v>127</v>
-      </c>
       <c r="Q7" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="R7" s="1" t="s">
         <v>132</v>
-      </c>
-      <c r="R7" s="1" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>256</v>
-      </c>
       <c r="D8" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G8" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="H8" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="H8" s="1" t="s">
-        <v>143</v>
-      </c>
       <c r="J8" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="K8" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="K8" s="1" t="s">
-        <v>136</v>
-      </c>
       <c r="N8" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="O8" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="O8" s="1" t="s">
-        <v>156</v>
-      </c>
       <c r="Q8" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="R8" s="1" t="s">
         <v>233</v>
-      </c>
-      <c r="R8" s="1" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>308</v>
-      </c>
       <c r="D9" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="E9" s="1" t="s">
-        <v>147</v>
-      </c>
       <c r="G9" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="H9" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="H9" s="1" t="s">
-        <v>205</v>
-      </c>
       <c r="J9" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="K9" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="K9" s="1" t="s">
-        <v>262</v>
-      </c>
       <c r="N9" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="O9" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="O9" s="1" t="s">
-        <v>202</v>
-      </c>
       <c r="Q9" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="R9" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="R9" s="1" t="s">
+      <c r="S9" s="1" t="s">
         <v>165</v>
-      </c>
-      <c r="S9" s="1" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A10" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>565</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>566</v>
-      </c>
       <c r="D10" s="1" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G10" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="H10" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="H10" s="1" t="s">
-        <v>221</v>
-      </c>
       <c r="J10" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="K10" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="K10" s="1" t="s">
+      <c r="L10" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="L10" s="1" t="s">
-        <v>318</v>
-      </c>
       <c r="N10" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="O10" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="O10" s="1" t="s">
-        <v>178</v>
-      </c>
       <c r="Q10" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="R10" s="1" t="s">
         <v>171</v>
-      </c>
-      <c r="R10" s="1" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>585</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>586</v>
-      </c>
       <c r="D11" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G11" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="H11" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="H11" s="1" t="s">
-        <v>239</v>
-      </c>
       <c r="J11" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="K11" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="K11" s="1" t="s">
-        <v>395</v>
-      </c>
       <c r="N11" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="O11" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="O11" s="1" t="s">
-        <v>180</v>
-      </c>
       <c r="Q11" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="R11" s="1" t="s">
         <v>175</v>
-      </c>
-      <c r="R11" s="1" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.45">
       <c r="D12" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="G12" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="H12" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="H12" s="1" t="s">
-        <v>241</v>
-      </c>
       <c r="J12" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="K12" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="K12" s="1" t="s">
-        <v>432</v>
-      </c>
       <c r="N12" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="O12" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="O12" s="1" t="s">
-        <v>397</v>
-      </c>
       <c r="Q12" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="R12" s="1" t="s">
         <v>271</v>
-      </c>
-      <c r="R12" s="1" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.45">
       <c r="D13" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="E13" s="1" t="s">
-        <v>152</v>
-      </c>
       <c r="G13" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="H13" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="H13" s="1" t="s">
-        <v>266</v>
-      </c>
       <c r="J13" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="K13" s="1" t="s">
         <v>438</v>
       </c>
-      <c r="K13" s="1" t="s">
-        <v>439</v>
-      </c>
       <c r="N13" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="O13" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="O13" s="1" t="s">
-        <v>192</v>
-      </c>
       <c r="Q13" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="R13" s="1" t="s">
         <v>338</v>
-      </c>
-      <c r="R13" s="1" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.45">
       <c r="D14" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G14" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="H14" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="H14" s="1" t="s">
-        <v>83</v>
-      </c>
       <c r="N14" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Q14" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="R14" s="1" t="s">
         <v>379</v>
-      </c>
-      <c r="R14" s="1" t="s">
-        <v>380</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.45">
       <c r="D15" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="E15" s="1" t="s">
-        <v>195</v>
-      </c>
       <c r="G15" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="H15" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="H15" s="1" t="s">
+      <c r="I15" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="I15" s="1" t="s">
-        <v>275</v>
-      </c>
       <c r="N15" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q15" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="R15" s="1" t="s">
         <v>381</v>
-      </c>
-      <c r="R15" s="1" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.45">
       <c r="D16" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="E16" s="1" t="s">
-        <v>223</v>
-      </c>
       <c r="G16" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="H16" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="H16" s="1" t="s">
-        <v>289</v>
-      </c>
       <c r="N16" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="O16" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="O16" s="1" t="s">
-        <v>320</v>
-      </c>
       <c r="P16" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="Q16" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="R16" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="17" spans="4:18" x14ac:dyDescent="0.45">
       <c r="D17" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="E17" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="E17" s="1" t="s">
-        <v>253</v>
-      </c>
       <c r="G17" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="H17" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="H17" s="1" t="s">
-        <v>295</v>
-      </c>
       <c r="N17" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="O17" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="O17" s="1" t="s">
-        <v>306</v>
-      </c>
       <c r="P17" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="Q17" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="R17" s="1" t="s">
         <v>384</v>
-      </c>
-      <c r="R17" s="1" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="18" spans="4:18" x14ac:dyDescent="0.45">
       <c r="D18" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="E18" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="E18" s="1" t="s">
-        <v>260</v>
-      </c>
       <c r="G18" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="H18" s="1" t="s">
         <v>475</v>
       </c>
-      <c r="H18" s="1" t="s">
-        <v>476</v>
-      </c>
       <c r="N18" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="O18" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="O18" s="1" t="s">
-        <v>389</v>
-      </c>
       <c r="Q18" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="R18" s="1" t="s">
         <v>386</v>
-      </c>
-      <c r="R18" s="1" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="19" spans="4:18" x14ac:dyDescent="0.45">
       <c r="D19" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G19" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="H19" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="H19" s="1" t="s">
-        <v>306</v>
-      </c>
       <c r="N19" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="O19" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="O19" s="1" t="s">
-        <v>411</v>
-      </c>
       <c r="Q19" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="R19" s="1" t="s">
         <v>429</v>
-      </c>
-      <c r="R19" s="1" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="20" spans="4:18" x14ac:dyDescent="0.45">
       <c r="D20" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="E20" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="E20" s="1" t="s">
-        <v>299</v>
-      </c>
       <c r="G20" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="H20" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="H20" s="1" t="s">
-        <v>270</v>
-      </c>
       <c r="N20" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="O20" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="O20" s="1" t="s">
-        <v>413</v>
-      </c>
       <c r="Q20" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="R20" s="1" t="s">
         <v>456</v>
-      </c>
-      <c r="R20" s="1" t="s">
-        <v>457</v>
       </c>
     </row>
     <row r="21" spans="4:18" x14ac:dyDescent="0.45">
       <c r="D21" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="E21" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="E21" s="1" t="s">
-        <v>401</v>
-      </c>
       <c r="G21" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="H21" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="H21" s="1" t="s">
-        <v>168</v>
-      </c>
       <c r="N21" s="1" t="s">
-        <v>414</v>
+        <v>595</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="P21" s="1" t="s">
-        <v>435</v>
+        <v>596</v>
       </c>
       <c r="Q21" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="R21" s="1" t="s">
         <v>314</v>
-      </c>
-      <c r="R21" s="1" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="22" spans="4:18" x14ac:dyDescent="0.45">
       <c r="D22" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="E22" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="F22" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="F22" s="1" t="s">
-        <v>418</v>
-      </c>
       <c r="G22" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="H22" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="H22" s="1" t="s">
-        <v>170</v>
-      </c>
       <c r="N22" s="1" t="s">
-        <v>433</v>
+        <v>413</v>
       </c>
       <c r="O22" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="P22" s="1" t="s">
         <v>434</v>
       </c>
       <c r="Q22" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="R22" s="1" t="s">
         <v>587</v>
-      </c>
-      <c r="R22" s="1" t="s">
-        <v>588</v>
       </c>
     </row>
     <row r="23" spans="4:18" x14ac:dyDescent="0.45">
       <c r="D23" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="E23" s="1" t="s">
         <v>470</v>
       </c>
-      <c r="E23" s="1" t="s">
-        <v>471</v>
-      </c>
       <c r="G23" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="H23" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="H23" s="1" t="s">
-        <v>192</v>
-      </c>
       <c r="I23" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>449</v>
+        <v>432</v>
       </c>
       <c r="O23" s="1" t="s">
-        <v>450</v>
+        <v>433</v>
       </c>
     </row>
     <row r="24" spans="4:18" x14ac:dyDescent="0.45">
       <c r="D24" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="E24" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="E24" s="1" t="s">
-        <v>480</v>
-      </c>
       <c r="G24" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="H24" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="H24" s="1" t="s">
-        <v>325</v>
-      </c>
       <c r="N24" s="1" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="O24" s="1" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
     </row>
     <row r="25" spans="4:18" x14ac:dyDescent="0.45">
       <c r="D25" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="E25" s="1" t="s">
         <v>504</v>
       </c>
-      <c r="E25" s="1" t="s">
-        <v>505</v>
-      </c>
       <c r="G25" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="H25" s="1" t="s">
         <v>545</v>
       </c>
-      <c r="H25" s="1" t="s">
+      <c r="I25" s="1" t="s">
         <v>546</v>
       </c>
-      <c r="I25" s="1" t="s">
-        <v>547</v>
-      </c>
       <c r="N25" s="1" t="s">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="O25" s="1" t="s">
-        <v>461</v>
+        <v>451</v>
       </c>
     </row>
     <row r="26" spans="4:18" x14ac:dyDescent="0.45">
       <c r="D26" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="E26" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="E26" s="1" t="s">
+      <c r="F26" s="1" t="s">
         <v>540</v>
       </c>
-      <c r="F26" s="1" t="s">
-        <v>541</v>
-      </c>
       <c r="N26" s="1" t="s">
-        <v>477</v>
+        <v>459</v>
       </c>
       <c r="O26" s="1" t="s">
-        <v>478</v>
+        <v>460</v>
       </c>
     </row>
     <row r="27" spans="4:18" x14ac:dyDescent="0.45">
       <c r="D27" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="E27" s="1" t="s">
         <v>542</v>
       </c>
-      <c r="E27" s="1" t="s">
+      <c r="F27" s="1" t="s">
         <v>543</v>
       </c>
-      <c r="F27" s="1" t="s">
-        <v>544</v>
-      </c>
       <c r="N27" s="1" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="O27" s="1" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
     </row>
     <row r="28" spans="4:18" x14ac:dyDescent="0.45">
       <c r="D28" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="E28" s="1" t="s">
         <v>578</v>
       </c>
-      <c r="E28" s="1" t="s">
-        <v>579</v>
-      </c>
       <c r="N28" s="1" t="s">
-        <v>569</v>
+        <v>480</v>
       </c>
       <c r="O28" s="1" t="s">
-        <v>570</v>
+        <v>481</v>
       </c>
     </row>
     <row r="29" spans="4:18" x14ac:dyDescent="0.45">
       <c r="D29" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="E29" s="1" t="s">
         <v>580</v>
       </c>
-      <c r="E29" s="1" t="s">
-        <v>581</v>
-      </c>
       <c r="N29" s="1" t="s">
-        <v>576</v>
+        <v>568</v>
       </c>
       <c r="O29" s="1" t="s">
-        <v>577</v>
+        <v>569</v>
       </c>
     </row>
     <row r="30" spans="4:18" x14ac:dyDescent="0.45">
       <c r="D30" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="E30" s="1" t="s">
         <v>589</v>
       </c>
-      <c r="E30" s="1" t="s">
-        <v>590</v>
-      </c>
       <c r="N30" s="1" t="s">
-        <v>567</v>
+        <v>575</v>
       </c>
       <c r="O30" s="1" t="s">
-        <v>568</v>
+        <v>576</v>
       </c>
     </row>
     <row r="31" spans="4:18" x14ac:dyDescent="0.45">
       <c r="N31" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="O31" s="1" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="32" spans="4:18" x14ac:dyDescent="0.45">
+      <c r="N32" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="O32" s="1" t="s">
         <v>563</v>
       </c>
-      <c r="O31" s="1" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="32" spans="4:18" x14ac:dyDescent="0.45">
-      <c r="P32" s="4" t="s">
-        <v>531</v>
-      </c>
     </row>
     <row r="33" spans="14:16" x14ac:dyDescent="0.45">
-      <c r="N33" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="O33" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="P33" s="1" t="s">
-        <v>501</v>
+      <c r="P33" s="4" t="s">
+        <v>530</v>
       </c>
     </row>
     <row r="34" spans="14:16" x14ac:dyDescent="0.45">
       <c r="N34" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="O34" s="1" t="s">
-        <v>184</v>
+        <v>181</v>
+      </c>
+      <c r="P34" s="1" t="s">
+        <v>500</v>
       </c>
     </row>
     <row r="35" spans="14:16" x14ac:dyDescent="0.45">
       <c r="N35" s="1" t="s">
-        <v>530</v>
+        <v>182</v>
       </c>
       <c r="O35" s="1" t="s">
-        <v>529</v>
+        <v>183</v>
       </c>
     </row>
     <row r="36" spans="14:16" x14ac:dyDescent="0.45">
       <c r="N36" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="O36" s="1" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="37" spans="14:16" x14ac:dyDescent="0.45">
+      <c r="N37" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="O37" s="1" t="s">
         <v>499</v>
-      </c>
-      <c r="O36" s="1" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="38" spans="14:16" x14ac:dyDescent="0.45">
-      <c r="N38" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="O38" s="1" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="39" spans="14:16" x14ac:dyDescent="0.45">
       <c r="N39" s="1" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="O39" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="40" spans="14:16" x14ac:dyDescent="0.45">
       <c r="N40" s="1" t="s">
-        <v>212</v>
+        <v>253</v>
       </c>
       <c r="O40" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="P40" s="1" t="s">
-        <v>440</v>
+        <v>252</v>
       </c>
     </row>
     <row r="41" spans="14:16" x14ac:dyDescent="0.45">
       <c r="N41" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="O41" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="P41" s="1" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="42" spans="14:16" x14ac:dyDescent="0.45">
+      <c r="N42" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="O42" s="1" t="s">
         <v>458</v>
-      </c>
-      <c r="O41" s="1" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="43" spans="14:16" x14ac:dyDescent="0.45">
-      <c r="N43" s="1" t="s">
-        <v>436</v>
-      </c>
-      <c r="O43" s="1" t="s">
-        <v>437</v>
       </c>
     </row>
     <row r="44" spans="14:16" x14ac:dyDescent="0.45">
       <c r="N44" s="1" t="s">
-        <v>261</v>
+        <v>435</v>
       </c>
       <c r="O44" s="1" t="s">
-        <v>262</v>
+        <v>436</v>
       </c>
     </row>
     <row r="45" spans="14:16" x14ac:dyDescent="0.45">
       <c r="N45" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="O45" s="1" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="46" spans="14:16" x14ac:dyDescent="0.45">
+      <c r="N46" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="O46" s="1" t="s">
         <v>438</v>
-      </c>
-      <c r="O45" s="1" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="47" spans="14:16" x14ac:dyDescent="0.45">
-      <c r="N47" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="O47" s="1" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="48" spans="14:16" x14ac:dyDescent="0.45">
       <c r="N48" s="1" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="O48" s="1" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
     </row>
     <row r="49" spans="14:16" x14ac:dyDescent="0.45">
       <c r="N49" s="1" t="s">
-        <v>226</v>
+        <v>302</v>
       </c>
       <c r="O49" s="1" t="s">
-        <v>227</v>
+        <v>303</v>
       </c>
     </row>
     <row r="50" spans="14:16" x14ac:dyDescent="0.45">
       <c r="N50" s="1" t="s">
-        <v>444</v>
+        <v>225</v>
       </c>
       <c r="O50" s="1" t="s">
-        <v>445</v>
+        <v>226</v>
       </c>
     </row>
     <row r="51" spans="14:16" x14ac:dyDescent="0.45">
       <c r="N51" s="1" t="s">
-        <v>453</v>
+        <v>443</v>
       </c>
       <c r="O51" s="1" t="s">
-        <v>454</v>
-      </c>
-      <c r="P51" s="1" t="s">
-        <v>575</v>
+        <v>444</v>
       </c>
     </row>
     <row r="52" spans="14:16" x14ac:dyDescent="0.45">
       <c r="N52" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="O52" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="P52" s="1" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="53" spans="14:16" x14ac:dyDescent="0.45">
+      <c r="N53" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="O53" s="1" t="s">
         <v>573</v>
-      </c>
-      <c r="O52" s="1" t="s">
-        <v>574</v>
       </c>
     </row>
   </sheetData>
@@ -5406,64 +5454,64 @@
   <sheetData>
     <row r="2" spans="1:3" ht="18" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>336</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="18" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>144</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="18" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>291</v>
-      </c>
       <c r="C4" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="18" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>309</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>427</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>428</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="18" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>488</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>489</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="18" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>490</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="C8" s="1" t="s">
         <v>491</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>492</v>
       </c>
     </row>
   </sheetData>
